--- a/public/templates/MARY_Plantilla_Mat_Presupuestados_ES.xlsx
+++ b/public/templates/MARY_Plantilla_Mat_Presupuestados_ES.xlsx
@@ -1,31 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dmarq\OneDrive\Desktop\New folder\ERP\mary-app\public\templates\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DFB88F0-E7E4-49F6-A1A2-45E3D6F2A1AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="36312" yWindow="25812" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="36312" yWindow="25812" windowWidth="23256" windowHeight="12456"/>
   </bookViews>
   <sheets>
-    <sheet name="Mat. Presupuestados" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Mat. Presupuestados" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
   <si>
     <t>PLANTILLA DE IMPORTACIÓN — MATERIALES PRESUPUESTADOS — MARY</t>
   </si>
@@ -33,7 +22,7 @@
     <t>Marquez Project Solutions LLC  ·  appmary.com</t>
   </si>
   <si>
-    <t>INSTRUCCIONES:  1. Código Material: debe coincidir EXACTAMENTE con el código registrado en el Catálogo de Materiales.  2. Nombre Material: referencia visual (no se importa).  3. Unidad y Cantidad Presupuestada son obligatorios.  4. Un material puede repetirse en varias filas si se usa en distintas actividades.</t>
+    <t>INSTRUCCIONES:  1. Código Material: debe coincidir EXACTAMENTE con el código registrado en el Catálogo de Materiales.  2. Nombre Material: referencia visual (no se importa).  3. Unidad y Cantidad Presupuestada son obligatorios.  4. Un material puede repetirse en varias filas si se usa en distintas actividades.  5. Costo Unitario (opcional): si va vacío se usa el precio del catálogo.  6. Código Actividad (opcional): código del presupuesto, ej. 01.04.001.</t>
   </si>
   <si>
     <t>Código Material*</t>
@@ -48,6 +37,12 @@
     <t>Cant. Presupuestada*</t>
   </si>
   <si>
+    <t>Costo Unitario</t>
+  </si>
+  <si>
+    <t>Código Actividad</t>
+  </si>
+  <si>
     <t>* Campos obligatorios  |  El Código Material debe existir en el Catálogo de Materiales de MARY</t>
   </si>
   <si>
@@ -58,6 +53,9 @@
   </si>
   <si>
     <t>und</t>
+  </si>
+  <si>
+    <t>01.04.001</t>
   </si>
   <si>
     <t>ml</t>
@@ -108,45 +106,45 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <color rgb="FFFFFFFF"/>
       <sz val="12"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
     </font>
     <font>
+      <color rgb="FF94A3B8"/>
       <sz val="9"/>
-      <color rgb="FF94A3B8"/>
       <name val="Arial"/>
     </font>
     <font>
+      <color rgb="FFFFFFFF"/>
       <sz val="8"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
+      <color rgb="FFFFFFFF"/>
       <sz val="9"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
     </font>
     <font>
+      <color rgb="FF475569"/>
       <sz val="8"/>
-      <color rgb="FF475569"/>
       <name val="Arial"/>
     </font>
     <font>
+      <color rgb="FF000000"/>
       <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -200,33 +198,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -234,7 +229,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -530,184 +525,199 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83984375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.55" defaultColWidth="8.83984375" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="4" max="6" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="4" t="s">
+    <row r="1" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-    </row>
-    <row r="2" spans="1:14" ht="14.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B1"/>
+      <c r="C1"/>
+      <c r="D1"/>
+      <c r="E1"/>
+    </row>
+    <row r="2" ht="14.05" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-    </row>
-    <row r="3" spans="1:14" ht="50.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="5" t="s">
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+    </row>
+    <row r="3" ht="50.05" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-    </row>
-    <row r="4" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="1" t="s">
+      <c r="B3"/>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+    </row>
+    <row r="4" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" s="8" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="6" t="s">
+      <c r="E4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-    </row>
-    <row r="6" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="9" t="s">
+      <c r="F4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="10" t="s">
+    </row>
+    <row r="5" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="B5"/>
+      <c r="C5"/>
+      <c r="D5"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="11">
+      <c r="B6" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="8">
         <v>50</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="9"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="11"/>
-      <c r="N7" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="9"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="11"/>
-      <c r="N8" s="8" t="s">
+      <c r="E6" s="8">
+        <v>8.5</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="6"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="8"/>
+      <c r="N7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="6"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="8"/>
+      <c r="N8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="6"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="8"/>
+      <c r="N9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="6"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="8"/>
+      <c r="N10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N15" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N16" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="9"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="11"/>
-      <c r="N9" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="9"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="11"/>
-      <c r="N10" s="8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="N11" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="N12" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="N13" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="N14" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="N15" s="8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="N16" s="8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="14:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="N17" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="18" spans="14:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="N18" s="8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="19" spans="14:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="N19" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="20" spans="14:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="N20" s="8" t="s">
+    <row r="17" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N17" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="14:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="N21" s="8" t="s">
+    <row r="18" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N18" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="14:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="N22" s="8" t="s">
+    <row r="19" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N19" t="s">
         <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N20" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="21" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N22" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A3:E3"/>
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A3:E3"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C7:C10" xr:uid="{EB0232F2-C3E6-4189-8076-41E7A266F90E}">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C10">
+      <formula1>$N$7:$N$22</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C7:C10">
       <formula1>$N$7:$N$22</formula1>
     </dataValidation>
   </dataValidations>
